--- a/artfynd/Norrbyskogens naturreservat artfynd.xlsx
+++ b/artfynd/Norrbyskogens naturreservat artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY170"/>
+  <dimension ref="A1:AZ170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114452236</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114452245</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416719</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80094695</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416712</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98430488</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1420,6 +1455,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417219</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416705</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1619,6 +1664,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416715</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1725,6 +1775,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417231</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416720</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1924,6 +1984,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416699</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2026,6 +2091,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416700</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2128,6 +2198,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416701</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2230,6 +2305,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416706</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2332,6 +2412,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416721</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2434,6 +2519,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416722</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2540,6 +2630,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417232</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2642,6 +2737,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416704</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2739,6 +2839,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416698</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2841,6 +2946,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416703</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2943,6 +3053,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416702</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3045,6 +3160,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416713</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3147,6 +3267,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416716</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3262,6 +3387,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122281874</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3368,6 +3498,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/244747</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3509,6 +3644,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998855</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3634,6 +3774,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86777031</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3736,6 +3881,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112989410</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3863,6 +4013,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998854</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3970,6 +4125,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998849</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4077,6 +4237,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998850</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4184,6 +4349,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998851</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4311,6 +4481,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998852</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4418,6 +4593,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998857</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4520,6 +4700,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416708</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4634,6 +4819,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80096845</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4748,6 +4938,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80100706</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4861,6 +5056,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112987911</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4978,6 +5178,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998858</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5085,6 +5290,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416707</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5187,6 +5397,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416709</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5289,6 +5504,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416710</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5386,6 +5606,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98416711</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5517,6 +5742,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69370470</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5648,6 +5878,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69370472</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5779,6 +6014,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69369918</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5910,6 +6150,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69370986</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6041,6 +6286,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69370988</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6164,6 +6414,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80096918</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6273,6 +6528,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77034199</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6382,6 +6642,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77034226</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6491,6 +6756,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77034193</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6596,6 +6866,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77034215</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6727,6 +7002,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69370469</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6858,6 +7138,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69369917</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6989,6 +7274,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69370985</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7120,6 +7410,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69369704</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7236,6 +7531,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75274160</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7347,6 +7647,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75282529</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7451,6 +7756,11 @@
       <c r="AY62" t="inlineStr">
         <is>
           <t>AKN0133 Norrbyskogen</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417214</t>
         </is>
       </c>
     </row>
@@ -7554,6 +7864,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80117774</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7658,6 +7973,11 @@
       <c r="AY64" t="inlineStr">
         <is>
           <t>AKN0133 Norrbyskogen</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417216</t>
         </is>
       </c>
     </row>
@@ -7766,6 +8086,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75274128</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7871,6 +8196,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75282597</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7980,6 +8310,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86713974</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8093,6 +8428,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112986419</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8200,6 +8540,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998859</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8306,6 +8651,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417215</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8412,6 +8762,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417213</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8520,6 +8875,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112986528</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8618,6 +8978,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75282539</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8732,6 +9097,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80097249</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8838,6 +9208,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417228</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8946,6 +9321,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106061142</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9047,6 +9427,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80117814</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9148,6 +9533,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80117827</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9262,6 +9652,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86703283</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9371,6 +9766,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86759137</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9472,6 +9872,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417202</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9573,6 +9978,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417229</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9689,6 +10099,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/244749</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9805,6 +10220,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/549346</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9904,6 +10324,11 @@
       <c r="AY85" t="inlineStr">
         <is>
           <t>AKN0133 Norrbyskogen</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417227</t>
         </is>
       </c>
     </row>
@@ -10012,6 +10437,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77034289</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10117,6 +10547,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80117728</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10233,6 +10668,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4994148</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10379,6 +10819,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998864</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10481,6 +10926,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112982603</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10583,6 +11033,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112985088</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10690,6 +11145,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998866</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10797,6 +11257,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998867</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10918,6 +11383,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998908</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11035,6 +11505,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106060010</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11143,6 +11618,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983065</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11250,6 +11730,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998871</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11351,6 +11836,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417225</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11483,6 +11973,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998863</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11615,6 +12110,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998872</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11747,6 +12247,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998873</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11879,6 +12384,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998869</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12011,6 +12521,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998870</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12121,6 +12636,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62911297</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12219,6 +12739,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983347</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12327,6 +12852,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983378</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12434,6 +12964,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998862</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12548,6 +13083,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57164070</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12665,6 +13205,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82841299</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12764,6 +13309,11 @@
       <c r="AY110" t="inlineStr">
         <is>
           <t>AKN0133 Norrbyskogen</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417199</t>
         </is>
       </c>
     </row>
@@ -12873,6 +13423,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77039713</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12982,6 +13537,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80117292</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13087,6 +13647,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80100739</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13192,6 +13757,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80100744</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13305,6 +13875,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112986542</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13411,6 +13986,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417218</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13517,6 +14097,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417224</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13618,6 +14203,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417200</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13724,6 +14314,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417221</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13825,6 +14420,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417207</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13926,6 +14526,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417223</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14033,6 +14638,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/25663761</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14142,6 +14752,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77039732</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14243,6 +14858,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417222</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14359,6 +14979,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/25663792</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14466,6 +15091,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/25671923</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14580,6 +15210,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91365827</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14700,6 +15335,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98429661</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14834,6 +15474,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98451561</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14953,6 +15598,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93389133</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15072,6 +15722,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93389123</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15191,6 +15846,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102595855</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15299,6 +15959,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983598</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15422,6 +16087,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82256434</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15530,6 +16200,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983691</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15639,6 +16314,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66440228</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15754,6 +16434,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82256406</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15855,6 +16540,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80097727</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15979,6 +16669,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80117493</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16091,6 +16786,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99203753</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16199,6 +16899,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112985534</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16332,6 +17037,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80100735</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16439,6 +17149,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418564</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16571,6 +17286,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418563</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16680,6 +17400,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77039648</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16811,6 +17536,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69370471</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16942,6 +17672,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69370987</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17043,6 +17778,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417211</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17144,6 +17884,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417208</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17252,6 +17997,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112984762</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17359,6 +18109,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998918</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17466,6 +18221,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998919</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17573,6 +18333,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998920</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17687,6 +18452,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121120529</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17791,6 +18561,11 @@
       <c r="AY155" t="inlineStr">
         <is>
           <t>AKN0133 Norrbyskogen</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417209</t>
         </is>
       </c>
     </row>
@@ -17908,6 +18683,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998924</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18009,6 +18789,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417220</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18129,6 +18914,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114536043</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18239,6 +19029,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114536067</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18340,6 +19135,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417206</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18467,6 +19267,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998921</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18579,6 +19384,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418562</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18685,6 +19495,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417204</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18786,6 +19601,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417205</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18918,6 +19738,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998922</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19029,6 +19854,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73075716</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19151,6 +19981,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418569</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19278,6 +20113,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418570</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19410,6 +20250,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418566</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19542,8 +20387,184 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418568</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>